--- a/data/sample_2_answer.xlsx
+++ b/data/sample_2_answer.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\port_k\portfolio_kweb\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\port_React _x\portfolio_kweb\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29A4430-EE85-45F2-AA12-081377F40283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA67F877-DC52-406A-8872-3A08D758018B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9948" yWindow="1320" windowWidth="12984" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="正解" sheetId="1" r:id="rId1"/>
@@ -44,13 +44,6 @@
     <t>正解</t>
   </si>
   <si>
-    <t>坂井</t>
-    <rPh sb="0" eb="2">
-      <t>サカイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>試験名</t>
   </si>
   <si>
@@ -58,6 +51,13 @@
   </si>
   <si>
     <t>氏名</t>
+  </si>
+  <si>
+    <t>武豊</t>
+    <rPh sb="0" eb="2">
+      <t>タケユタカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -115,10 +115,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -689,19 +688,19 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>4</v>
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>2</v>
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
